--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>1</v>
       </c>
       <c r="K15" s="14">
+        <v>100</v>
+      </c>
+      <c r="L15" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M15" s="14">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="M15" s="14">
-        <v>-50</v>
-      </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>4</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-75</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
+        <v>8</v>
+      </c>
+      <c r="G16" s="15">
         <v>7</v>
       </c>
-      <c r="G16" s="15">
-        <v>10</v>
-      </c>
       <c r="H16" s="14">
-        <v>-30</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I16" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
         <v>11</v>
       </c>
       <c r="K16" s="14">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-42.857142857142</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M16" s="14">
-        <v>-65.217391304347</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.160583941605</v>
+        <v>-93.209876543209</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>66.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>42.857142857142</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K17" s="14">
-        <v>27.272727272727</v>
+        <v>10</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>75</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-45.098039215686</v>
+        <v>-44.067796610169</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>100</v>
       </c>
       <c r="F18" s="15">
+        <v>10</v>
+      </c>
+      <c r="G18" s="15">
         <v>6</v>
       </c>
-      <c r="G18" s="15">
-        <v>5</v>
-      </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-71.428571428571</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.818181818181</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.736842105263</v>
+        <v>-92.424242424242</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>11.111111111111</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-25</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="I19" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J19" s="15">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.703703703703</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L19" s="14">
-        <v>-56.666666666666</v>
+        <v>-60.563380281690</v>
       </c>
       <c r="M19" s="14">
-        <v>-23.529411764705</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N19" s="14">
-        <v>-40.909090909090</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="C20" s="15">
+        <v>3</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L20" s="14">
-        <v>-72.727272727272</v>
+        <v>-65.384615384615</v>
       </c>
       <c r="M20" s="14">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-96</v>
+        <v>-94.578313253012</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,72 +1142,72 @@
         <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>5.882352941176</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.448275862068</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J21" s="17">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="K21" s="18">
-        <v>1.351351351351</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="L21" s="18">
-        <v>-48.979591836734</v>
+        <v>-46.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>-39.516129032258</v>
+        <v>-30.597014925373</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.029940119760</v>
+        <v>-83.769633507853</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
         <v>2</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>3</v>
-      </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
         <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="L22" s="14">
+        <v>400</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.461538461538</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F24" s="15">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G24" s="15">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H24" s="14">
-        <v>-24.489795918367</v>
+        <v>-20</v>
       </c>
       <c r="I24" s="15">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="J24" s="15">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.571428571428</v>
+        <v>-1.265822784810</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.461538461538</v>
+        <v>-34.453781512605</v>
       </c>
       <c r="M24" s="14">
-        <v>-41.284403669724</v>
+        <v>-32.173913043478</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="15">
+        <v>4</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F25" s="15">
         <v>8</v>
       </c>
-      <c r="E25" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="F25" s="15">
-        <v>10</v>
-      </c>
       <c r="G25" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-52.380952380952</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I25" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.769230769230</v>
+        <v>-30</v>
       </c>
       <c r="L25" s="14">
-        <v>-66.037735849056</v>
+        <v>-63.793103448275</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>-58.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F26" s="15">
+        <v>40</v>
+      </c>
+      <c r="G26" s="15">
         <v>36</v>
       </c>
-      <c r="G26" s="15">
-        <v>30</v>
-      </c>
       <c r="H26" s="14">
-        <v>20</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I26" s="15">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="J26" s="15">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>16.279069767441</v>
+        <v>8.620689655172</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.960784313725</v>
+        <v>18.867924528301</v>
       </c>
       <c r="M26" s="14">
-        <v>-21.875</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
         <v>0</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>3</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-66.666666666666</v>
-      </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="14">
         <v>50</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
+        <v>3</v>
+      </c>
+      <c r="J15" s="15">
         <v>2</v>
       </c>
-      <c r="J15" s="15">
-        <v>1</v>
-      </c>
       <c r="K15" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>14.285714285714</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.888888888888</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M16" s="14">
-        <v>-57.692307692307</v>
+        <v>-56.25</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.209876543209</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-37.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>-5.263157894736</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K17" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="M17" s="14">
-        <v>83.333333333333</v>
+        <v>60.869565217391</v>
       </c>
       <c r="N17" s="14">
-        <v>-44.067796610169</v>
+        <v>-43.939393939393</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>66.666666666666</v>
+        <v>80</v>
       </c>
       <c r="I18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L18" s="14">
-        <v>-58.333333333333</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="M18" s="14">
-        <v>-70.588235294117</v>
+        <v>-68.292682926829</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.424242424242</v>
+        <v>-91.216216216216</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>-81.818181818181</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="14">
-        <v>-51.515151515151</v>
+        <v>-40.625</v>
       </c>
       <c r="I19" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J19" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.315789473684</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L19" s="14">
-        <v>-60.563380281690</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="M19" s="14">
-        <v>-22.222222222222</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.857142857142</v>
+        <v>-41.379310344827</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
         <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L20" s="14">
-        <v>-65.384615384615</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.578313253012</v>
+        <v>-95.135135135135</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>14</v>
+      </c>
+      <c r="D21" s="17">
         <v>18</v>
       </c>
-      <c r="D21" s="17">
-        <v>21</v>
-      </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.857142857142</v>
+        <v>-15.068493150684</v>
       </c>
       <c r="I21" s="17">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="J21" s="17">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.105263157894</v>
+        <v>-2.654867256637</v>
       </c>
       <c r="L21" s="18">
-        <v>-46.857142857142</v>
+        <v>-46.078431372549</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.597014925373</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.769633507853</v>
+        <v>-83.358547655068</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1265,34 +1265,34 @@
         <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>22.222222222222</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F24" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G24" s="15">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H24" s="14">
-        <v>-20</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="I24" s="15">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J24" s="15">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="K24" s="14">
-        <v>-1.265822784810</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.453781512605</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M24" s="14">
-        <v>-32.173913043478</v>
+        <v>-31.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>350</v>
       </c>
       <c r="F25" s="15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-52.941176470588</v>
+        <v>6.25</v>
       </c>
       <c r="I25" s="15">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J25" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K25" s="14">
-        <v>-30</v>
+        <v>-6.25</v>
       </c>
       <c r="L25" s="14">
-        <v>-63.793103448275</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-13.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F26" s="15">
+        <v>44</v>
+      </c>
+      <c r="G26" s="15">
         <v>40</v>
       </c>
-      <c r="G26" s="15">
-        <v>36</v>
-      </c>
       <c r="H26" s="14">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="I26" s="15">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J26" s="15">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K26" s="14">
-        <v>8.620689655172</v>
+        <v>14.925373134328</v>
       </c>
       <c r="L26" s="14">
-        <v>18.867924528301</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.181818181818</v>
+        <v>-13.483146067415</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
+        <v>50</v>
+      </c>
+      <c r="I27" s="15">
+        <v>3</v>
+      </c>
+      <c r="J27" s="15">
+        <v>5</v>
+      </c>
+      <c r="K27" s="14">
+        <v>-40</v>
+      </c>
+      <c r="L27" s="14">
         <v>0</v>
-      </c>
-      <c r="I27" s="15">
-        <v>2</v>
-      </c>
-      <c r="J27" s="15">
-        <v>4</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>66.666666666666</v>
+        <v>500</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>133.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>50</v>
       </c>
       <c r="L31" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I16" s="15">
+        <v>15</v>
+      </c>
+      <c r="J16" s="15">
         <v>14</v>
       </c>
-      <c r="J16" s="15">
-        <v>13</v>
-      </c>
       <c r="K16" s="14">
-        <v>7.692307692307</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.130434782608</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M16" s="14">
-        <v>-56.25</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.857142857142</v>
+        <v>-93.055555555555</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-42.857142857142</v>
+        <v>400</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-29.166666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.128205128205</v>
+        <v>-12.5</v>
       </c>
       <c r="M17" s="14">
-        <v>60.869565217391</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N17" s="14">
-        <v>-43.939393939393</v>
+        <v>-41.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
         <v>11</v>
       </c>
       <c r="K18" s="14">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L18" s="14">
-        <v>-55.172413793103</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="M18" s="14">
-        <v>-68.292682926829</v>
+        <v>-68.888888888888</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.216216216216</v>
+        <v>-91.812865497076</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>7</v>
+      </c>
+      <c r="D19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="15">
-        <v>6</v>
-      </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>40</v>
       </c>
       <c r="F19" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-40.625</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I19" s="15">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J19" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" s="14">
-        <v>-22.727272727272</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="L19" s="14">
-        <v>-58.536585365853</v>
+        <v>-57.731958762886</v>
       </c>
       <c r="M19" s="14">
-        <v>-22.727272727272</v>
+        <v>-18</v>
       </c>
       <c r="N19" s="14">
-        <v>-41.379310344827</v>
+        <v>-31.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>3</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>50</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L20" s="14">
-        <v>-67.857142857142</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="M20" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.135135135135</v>
+        <v>-93.969849246231</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>112.5</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.068493150684</v>
+        <v>9.375</v>
       </c>
       <c r="I21" s="17">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="J21" s="17">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.654867256637</v>
+        <v>4.958677685950</v>
       </c>
       <c r="L21" s="18">
-        <v>-46.078431372549</v>
+        <v>-46.861924686192</v>
       </c>
       <c r="M21" s="18">
-        <v>-33.333333333333</v>
+        <v>-30.978260869565</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.358547655068</v>
+        <v>-82.506887052341</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>25</v>
       </c>
       <c r="L22" s="14">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
         <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.888888888888</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G24" s="15">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>-21.276595744680</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="I24" s="15">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J24" s="15">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.278350515463</v>
+        <v>-14.782608695652</v>
       </c>
       <c r="L24" s="14">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M24" s="14">
-        <v>-31.25</v>
+        <v>-28.985507246376</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>350</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>6.25</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I25" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K25" s="14">
-        <v>-6.25</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L25" s="14">
-        <v>-54.545454545454</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>55.555555555555</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
         <v>44</v>
       </c>
       <c r="G26" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="14">
-        <v>10</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I26" s="15">
+        <v>88</v>
+      </c>
+      <c r="J26" s="15">
         <v>77</v>
       </c>
-      <c r="J26" s="15">
-        <v>67</v>
-      </c>
       <c r="K26" s="14">
-        <v>14.925373134328</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="14">
-        <v>22.222222222222</v>
+        <v>18.918918918918</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.483146067415</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,31 +1385,31 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I28" s="15">
         <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="14">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="14">
         <v>-50</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>14.285714285714</v>
+        <v>80</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>7.142857142857</v>
+        <v>6.25</v>
       </c>
       <c r="L16" s="14">
-        <v>-44.444444444444</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="M16" s="14">
-        <v>-57.142857142857</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.055555555555</v>
+        <v>-93.032786885245</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
       <c r="E17" s="14">
-        <v>400</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
         <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J17" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K17" s="14">
-        <v>10.526315789473</v>
+        <v>9.302325581395</v>
       </c>
       <c r="L17" s="14">
-        <v>-12.5</v>
+        <v>-14.545454545454</v>
       </c>
       <c r="M17" s="14">
-        <v>61.538461538461</v>
+        <v>67.857142857142</v>
       </c>
       <c r="N17" s="14">
-        <v>-41.666666666666</v>
+        <v>-44.705882352941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-57.575757575757</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M18" s="14">
-        <v>-68.888888888888</v>
+        <v>-70.833333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.812865497076</v>
+        <v>-92.746113989637</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>40</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="15">
         <v>25</v>
@@ -1075,22 +1075,22 @@
         <v>-19.354838709677</v>
       </c>
       <c r="I19" s="15">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J19" s="15">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.326530612244</v>
+        <v>-12.068965517241</v>
       </c>
       <c r="L19" s="14">
-        <v>-57.731958762886</v>
+        <v>-54.054054054054</v>
       </c>
       <c r="M19" s="14">
-        <v>-18</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="N19" s="14">
-        <v>-31.666666666666</v>
+        <v>-23.880597014925</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>3</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>200</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J20" s="15">
         <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>71.428571428571</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
-        <v>-61.290322580645</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.969849246231</v>
+        <v>-93.607305936073</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>112.5</v>
+        <v>-10</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>9.375</v>
+        <v>7.462686567164</v>
       </c>
       <c r="I21" s="17">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="J21" s="17">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="K21" s="18">
-        <v>4.958677685950</v>
+        <v>3.546099290780</v>
       </c>
       <c r="L21" s="18">
-        <v>-46.861924686192</v>
+        <v>-44.274809160305</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.978260869565</v>
+        <v>-27</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.506887052341</v>
+        <v>-82.129742962056</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
+        <v>6</v>
+      </c>
+      <c r="J22" s="15">
         <v>5</v>
       </c>
-      <c r="J22" s="15">
-        <v>4</v>
-      </c>
       <c r="K22" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L22" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M22" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="15">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" s="15">
         <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.758620689655</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I24" s="15">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J24" s="15">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.782608695652</v>
+        <v>-17.1875</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.363636363636</v>
+        <v>-38.728323699422</v>
       </c>
       <c r="M24" s="14">
-        <v>-28.985507246376</v>
+        <v>-28.378378378378</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-9.523809523809</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K25" s="14">
-        <v>-12.820512820512</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="L25" s="14">
-        <v>-55.263157894736</v>
+        <v>-54.216867469879</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H26" s="14">
-        <v>-4.347826086956</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J26" s="15">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K26" s="14">
-        <v>14.285714285714</v>
+        <v>23.170731707317</v>
       </c>
       <c r="L26" s="14">
-        <v>18.918918918918</v>
+        <v>20.238095238095</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.333333333333</v>
+        <v>-9.009009009009</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,13 +1385,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>5</v>
@@ -1403,16 +1403,16 @@
         <v>150</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
         <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>14.285714285714</v>
+        <v>-10</v>
       </c>
       <c r="L28" s="14">
-        <v>14.285714285714</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -905,16 +905,16 @@
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="15">
+        <v>7</v>
+      </c>
+      <c r="G16" s="15">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="15">
-        <v>9</v>
-      </c>
-      <c r="G16" s="15">
-        <v>5</v>
-      </c>
-      <c r="H16" s="14">
-        <v>80</v>
-      </c>
       <c r="I16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="14">
-        <v>6.25</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.285714285714</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-56.410256410256</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.032786885245</v>
+        <v>-92.775665399239</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
         <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>60</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-9.523809523809</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I17" s="15">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J17" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K17" s="14">
-        <v>9.302325581395</v>
+        <v>14.583333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-14.545454545454</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="M17" s="14">
-        <v>67.857142857142</v>
+        <v>61.764705882352</v>
       </c>
       <c r="N17" s="14">
-        <v>-44.705882352941</v>
+        <v>-40.217391304347</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
+        <v>2</v>
+      </c>
+      <c r="G18" s="15">
         <v>8</v>
       </c>
-      <c r="G18" s="15">
-        <v>6</v>
-      </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L18" s="14">
-        <v>-58.823529411764</v>
+        <v>-62.162162162162</v>
       </c>
       <c r="M18" s="14">
-        <v>-70.833333333333</v>
+        <v>-73.076923076923</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.746113989637</v>
+        <v>-93.457943925233</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>-19.354838709677</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I19" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J19" s="15">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K19" s="14">
-        <v>-12.068965517241</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="L19" s="14">
-        <v>-54.054054054054</v>
+        <v>-52.586206896551</v>
       </c>
       <c r="M19" s="14">
-        <v>-5.555555555555</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="N19" s="14">
-        <v>-23.880597014925</v>
+        <v>-24.657534246575</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>4</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
         <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L20" s="14">
-        <v>-54.838709677419</v>
+        <v>-56.25</v>
       </c>
       <c r="M20" s="14">
-        <v>-48.148148148148</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.607305936073</v>
+        <v>-94.017094017094</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-10</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>7.462686567164</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="I21" s="17">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>3.546099290780</v>
+        <v>0.625</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.274809160305</v>
+        <v>-42.086330935251</v>
       </c>
       <c r="M21" s="18">
-        <v>-27</v>
+        <v>-25.462962962963</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.129742962056</v>
+        <v>-81.828442437923</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
-      </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L22" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G24" s="15">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.482758620689</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="I24" s="15">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="J24" s="15">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="K24" s="14">
-        <v>-17.1875</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.728323699422</v>
+        <v>-35.263157894736</v>
       </c>
       <c r="M24" s="14">
-        <v>-28.378378378378</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>4</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>17.647058823529</v>
+        <v>6.25</v>
       </c>
       <c r="I25" s="15">
         <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.627906976744</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L25" s="14">
-        <v>-54.216867469879</v>
+        <v>-57.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>160</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H26" s="14">
-        <v>33.333333333333</v>
+        <v>32.352941176470</v>
       </c>
       <c r="I26" s="15">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J26" s="15">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K26" s="14">
-        <v>23.170731707317</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L26" s="14">
-        <v>20.238095238095</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M26" s="14">
-        <v>-9.009009009009</v>
+        <v>-13.6</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L27" s="14">
         <v>0</v>
-      </c>
-      <c r="L27" s="14">
-        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
         <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="L28" s="14">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,11 +1496,11 @@
       <c r="L29" s="14">
         <v>0</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>100</v>
       </c>
       <c r="N29" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1537,11 +1537,11 @@
       <c r="L30" s="14">
         <v>-50</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>0</v>
       </c>
       <c r="N30" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1634,8 +1634,8 @@
       <c r="K33" s="14">
         <v>-100</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="14">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="C15" s="15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="15">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N15" s="14">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>5.555555555555</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L16" s="14">
-        <v>-36.666666666666</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.282051282051</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.775665399239</v>
+        <v>-92.982456140350</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>6</v>
+      </c>
+      <c r="D17" s="15">
         <v>8</v>
       </c>
-      <c r="D17" s="15">
-        <v>5</v>
-      </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>22.222222222222</v>
+        <v>26.315789473684</v>
       </c>
       <c r="I17" s="15">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J17" s="15">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
-        <v>14.583333333333</v>
+        <v>8.928571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.779661016949</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="M17" s="14">
-        <v>61.764705882352</v>
+        <v>60.526315789473</v>
       </c>
       <c r="N17" s="14">
-        <v>-40.217391304347</v>
+        <v>-35.789473684210</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-75</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="14">
-        <v>-62.162162162162</v>
+        <v>-65.853658536585</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.076923076923</v>
+        <v>-74.545454545454</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.457943925233</v>
+        <v>-94.092827004219</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F19" s="15">
+        <v>25</v>
+      </c>
+      <c r="G19" s="15">
+        <v>25</v>
+      </c>
+      <c r="H19" s="14">
         <v>0</v>
       </c>
-      <c r="F19" s="15">
-        <v>24</v>
-      </c>
-      <c r="G19" s="15">
-        <v>23</v>
-      </c>
-      <c r="H19" s="14">
-        <v>4.347826086956</v>
-      </c>
       <c r="I19" s="15">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J19" s="15">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.836065573770</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="L19" s="14">
-        <v>-52.586206896551</v>
+        <v>-51.2</v>
       </c>
       <c r="M19" s="14">
-        <v>-3.508771929824</v>
+        <v>1.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-24.657534246575</v>
+        <v>-23.75</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I20" s="15">
+        <v>19</v>
+      </c>
+      <c r="J20" s="15">
         <v>14</v>
       </c>
-      <c r="J20" s="15">
-        <v>11</v>
-      </c>
       <c r="K20" s="14">
-        <v>27.272727272727</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L20" s="14">
-        <v>-56.25</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="M20" s="14">
-        <v>-51.724137931034</v>
+        <v>-40.625</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.017094017094</v>
+        <v>-92.490118577075</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.842105263157</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.076923076923</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="I21" s="17">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="K21" s="18">
-        <v>0.625</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="L21" s="18">
-        <v>-42.086330935251</v>
+        <v>-39.799331103678</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.462962962963</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.828442437923</v>
+        <v>-81.269510926118</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>2</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" s="15">
         <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M22" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F24" s="15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" s="15">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.230769230769</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="I24" s="15">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="J24" s="15">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.583333333333</v>
+        <v>-15.822784810126</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.263157894736</v>
+        <v>-38.990825688073</v>
       </c>
       <c r="M24" s="14">
-        <v>-24.074074074074</v>
+        <v>-22.674418604651</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
         <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>6.25</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I25" s="15">
         <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K25" s="14">
-        <v>-17.391304347826</v>
+        <v>-24</v>
       </c>
       <c r="L25" s="14">
-        <v>-57.777777777777</v>
+        <v>-64.814814814814</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-40</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G26" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>32.352941176470</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I26" s="15">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="J26" s="15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K26" s="14">
-        <v>17.391304347826</v>
+        <v>19</v>
       </c>
       <c r="L26" s="14">
-        <v>16.129032258064</v>
+        <v>17.821782178217</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.6</v>
+        <v>-12.5</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="15">
         <v>6</v>
       </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>30</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>30</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.761904761904</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.393939393939</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M16" s="14">
-        <v>-52.380952380952</v>
+        <v>-51.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.982456140350</v>
+        <v>-92.880258899676</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>40</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>26.315789473684</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I17" s="15">
+        <v>69</v>
+      </c>
+      <c r="J17" s="15">
         <v>61</v>
       </c>
-      <c r="J17" s="15">
-        <v>56</v>
-      </c>
       <c r="K17" s="14">
-        <v>8.928571428571</v>
+        <v>13.114754098360</v>
       </c>
       <c r="L17" s="14">
-        <v>-1.612903225806</v>
+        <v>-1.428571428571</v>
       </c>
       <c r="M17" s="14">
-        <v>60.526315789473</v>
+        <v>81.578947368421</v>
       </c>
       <c r="N17" s="14">
-        <v>-35.789473684210</v>
+        <v>-37.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-88.888888888888</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="L18" s="14">
-        <v>-65.853658536585</v>
+        <v>-63.043478260869</v>
       </c>
       <c r="M18" s="14">
-        <v>-74.545454545454</v>
+        <v>-72.580645161290</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.092827004219</v>
+        <v>-93.511450381679</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>8</v>
+      </c>
+      <c r="D19" s="15">
         <v>6</v>
       </c>
-      <c r="D19" s="15">
-        <v>8</v>
-      </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I19" s="15">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J19" s="15">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.594202898550</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-51.2</v>
+        <v>-45.3125</v>
       </c>
       <c r="M19" s="14">
-        <v>1.666666666666</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="N19" s="14">
-        <v>-23.75</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>66.666666666666</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>37.5</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="15">
         <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>35.714285714285</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L20" s="14">
-        <v>-42.424242424242</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="M20" s="14">
-        <v>-40.625</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.490118577075</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.816901408450</v>
+        <v>-9.876543209876</v>
       </c>
       <c r="I21" s="17">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="J21" s="17">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.173913043478</v>
+        <v>0.495049504950</v>
       </c>
       <c r="L21" s="18">
-        <v>-39.799331103678</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.413793103448</v>
+        <v>-21.923076923076</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.269510926118</v>
+        <v>-80.703422053231</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>166.666666666667</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G24" s="15">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>-26.229508196721</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="I24" s="15">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="J24" s="15">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.822784810126</v>
+        <v>-16.184971098265</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.990825688073</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="M24" s="14">
-        <v>-22.674418604651</v>
+        <v>-19.889502762430</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-55.555555555555</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="I25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K25" s="14">
-        <v>-24</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.814814814814</v>
+        <v>-67.213114754098</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>25</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>27.272727272727</v>
+        <v>34.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J26" s="15">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K26" s="14">
-        <v>19</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L26" s="14">
-        <v>17.821782178217</v>
+        <v>25.925925925925</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.5</v>
+        <v>-12.258064516129</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>13</v>
@@ -1453,7 +1453,7 @@
         <v>8.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>8.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
@@ -914,19 +914,19 @@
         <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M15" s="14">
         <v>25</v>
       </c>
       <c r="N15" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
         <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.347826086956</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.888888888888</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.111111111111</v>
+        <v>-51.063829787234</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.880258899676</v>
+        <v>-93.051359516616</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,54 +975,54 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
         <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>40</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
         <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>8.695652173913</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I17" s="15">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J17" s="15">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K17" s="14">
-        <v>13.114754098360</v>
+        <v>12.121212121212</v>
       </c>
       <c r="L17" s="14">
-        <v>-1.428571428571</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="M17" s="14">
-        <v>81.578947368421</v>
+        <v>72.093023255813</v>
       </c>
       <c r="N17" s="14">
-        <v>-37.272727272727</v>
+        <v>-39.837398373983</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
       <c r="E18" s="14">
-        <v>-40</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>3</v>
@@ -1037,19 +1037,19 @@
         <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" s="14">
-        <v>-32</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L18" s="14">
-        <v>-63.043478260869</v>
+        <v>-65.306122448979</v>
       </c>
       <c r="M18" s="14">
-        <v>-72.580645161290</v>
+        <v>-75.362318840579</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.511450381679</v>
+        <v>-93.992932862190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H19" s="14">
-        <v>7.692307692307</v>
+        <v>10</v>
       </c>
       <c r="I19" s="15">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J19" s="15">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.666666666666</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L19" s="14">
-        <v>-45.3125</v>
+        <v>-46.762589928057</v>
       </c>
       <c r="M19" s="14">
-        <v>-2.777777777777</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="N19" s="14">
-        <v>-22.222222222222</v>
+        <v>-26.732673267326</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="14">
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>42.857142857142</v>
+        <v>46.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-45.945945945945</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M20" s="14">
-        <v>-44.444444444444</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.592592592592</v>
+        <v>-92.387543252595</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.876543209876</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I21" s="17">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="J21" s="17">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="K21" s="18">
-        <v>0.495049504950</v>
+        <v>-0.921658986175</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.956521739130</v>
+        <v>-38.746438746438</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.923076923076</v>
+        <v>-23.487544483985</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.703422053231</v>
+        <v>-81.123792800702</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,10 +1189,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
         <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G24" s="15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H24" s="14">
-        <v>-20.689655172413</v>
+        <v>-15</v>
       </c>
       <c r="I24" s="15">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J24" s="15">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K24" s="14">
-        <v>-16.184971098265</v>
+        <v>-15.957446808510</v>
       </c>
       <c r="L24" s="14">
-        <v>-40.816326530612</v>
+        <v>-39.230769230769</v>
       </c>
       <c r="M24" s="14">
-        <v>-19.889502762430</v>
+        <v>-17.277486910994</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>-64.705882352941</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="I25" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J25" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.571428571428</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="L25" s="14">
-        <v>-67.213114754098</v>
+        <v>-65.116279069767</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>41.666666666666</v>
+        <v>220</v>
       </c>
       <c r="F26" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15">
         <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>34.285714285714</v>
+        <v>40</v>
       </c>
       <c r="I26" s="15">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J26" s="15">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K26" s="14">
-        <v>21.428571428571</v>
+        <v>29.059829059829</v>
       </c>
       <c r="L26" s="14">
-        <v>25.925925925925</v>
+        <v>37.272727272727</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.258064516129</v>
+        <v>-9.036144578313</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="L27" s="14">
         <v>-12.5</v>
-      </c>
-      <c r="L27" s="14">
-        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>5</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I28" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>8.333333333333</v>
+        <v>20</v>
       </c>
       <c r="L28" s="14">
-        <v>-13.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N15" s="14">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>-8</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L16" s="14">
-        <v>-39.473684210526</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="M16" s="14">
-        <v>-51.063829787234</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.051359516616</v>
+        <v>-92.877492877492</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H17" s="14">
-        <v>13.043478260869</v>
+        <v>15</v>
       </c>
       <c r="I17" s="15">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J17" s="15">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K17" s="14">
-        <v>12.121212121212</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L17" s="14">
-        <v>-3.896103896103</v>
+        <v>-3.614457831325</v>
       </c>
       <c r="M17" s="14">
-        <v>72.093023255813</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-39.837398373983</v>
+        <v>-40.298507462686</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-78.571428571428</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-39.285714285714</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-65.306122448979</v>
+        <v>-62.745098039215</v>
       </c>
       <c r="M18" s="14">
-        <v>-75.362318840579</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.992932862190</v>
+        <v>-93.870967741935</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>-70</v>
       </c>
       <c r="F19" s="15">
         <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14">
-        <v>10</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I19" s="15">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J19" s="15">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.128205128205</v>
+        <v>-12.5</v>
       </c>
       <c r="L19" s="14">
-        <v>-46.762589928057</v>
+        <v>-49.006622516556</v>
       </c>
       <c r="M19" s="14">
-        <v>-2.631578947368</v>
+        <v>-14.444444444444</v>
       </c>
       <c r="N19" s="14">
-        <v>-26.732673267326</v>
+        <v>-29.357798165137</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>46.666666666666</v>
+        <v>38.888888888888</v>
       </c>
       <c r="L20" s="14">
-        <v>-47.619047619047</v>
+        <v>-45.652173913043</v>
       </c>
       <c r="M20" s="14">
-        <v>-43.589743589743</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.387543252595</v>
+        <v>-92.012779552715</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.666666666666</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.157894736842</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="I21" s="17">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="J21" s="17">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.921658986175</v>
+        <v>-2.510460251046</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.746438746438</v>
+        <v>-38.684210526315</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.487544483985</v>
+        <v>-25.08038585209</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.123792800702</v>
+        <v>-81.041497152156</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
         <v>166.666666666667</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>24</v>
+      </c>
+      <c r="D24" s="15">
         <v>13</v>
       </c>
-      <c r="D24" s="15">
-        <v>15</v>
-      </c>
       <c r="E24" s="14">
-        <v>-13.333333333333</v>
+        <v>84.615384615384</v>
       </c>
       <c r="F24" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G24" s="15">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H24" s="14">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I24" s="15">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="J24" s="15">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.957446808510</v>
+        <v>-9.452736318407</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.230769230769</v>
+        <v>-34.296028880866</v>
       </c>
       <c r="M24" s="14">
-        <v>-17.277486910994</v>
+        <v>-9.452736318407</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>-61.111111111111</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I25" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J25" s="15">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.229508196721</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="L25" s="14">
-        <v>-65.116279069767</v>
+        <v>-63.235294117647</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>40</v>
+        <v>64.516129032258</v>
       </c>
       <c r="I26" s="15">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J26" s="15">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K26" s="14">
-        <v>29.059829059829</v>
+        <v>30.081300813008</v>
       </c>
       <c r="L26" s="14">
-        <v>37.272727272727</v>
+        <v>31.147540983606</v>
       </c>
       <c r="M26" s="14">
-        <v>-9.036144578313</v>
+        <v>-10.614525139664</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K27" s="14">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>5</v>
-      </c>
-      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="E28" s="14">
-        <v>66.666666666666</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>9</v>
@@ -1444,16 +1444,16 @@
         <v>80</v>
       </c>
       <c r="I28" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J28" s="15">
         <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L28" s="14">
-        <v>20</v>
+        <v>31.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" s="14">
         <v>-71.428571428571</v>
@@ -1538,7 +1538,7 @@
         <v>-50</v>
       </c>
       <c r="M30" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="14">
         <v>-85.714285714285</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M15" s="14">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-40</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>-10.714285714285</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L16" s="14">
-        <v>-40.476190476190</v>
+        <v>-41.304347826087</v>
       </c>
       <c r="M16" s="14">
-        <v>-50.980392156862</v>
+        <v>-48.076923076923</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.877492877492</v>
+        <v>-92.8</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>15</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I17" s="15">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J17" s="15">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K17" s="14">
-        <v>17.647058823529</v>
+        <v>17.567567567567</v>
       </c>
       <c r="L17" s="14">
-        <v>-3.614457831325</v>
+        <v>-7.446808510638</v>
       </c>
       <c r="M17" s="14">
-        <v>66.666666666666</v>
+        <v>77.551020408163</v>
       </c>
       <c r="N17" s="14">
-        <v>-40.298507462686</v>
+        <v>-41.216216216216</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-58.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
         <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-36.666666666666</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-62.745098039215</v>
+        <v>-60</v>
       </c>
       <c r="M18" s="14">
-        <v>-75</v>
+        <v>-73.809523809523</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.870967741935</v>
+        <v>-93.432835820895</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.518518518518</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J19" s="15">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K19" s="14">
-        <v>-12.5</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L19" s="14">
-        <v>-49.006622516556</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.444444444444</v>
+        <v>-13.829787234042</v>
       </c>
       <c r="N19" s="14">
-        <v>-29.357798165137</v>
+        <v>-31.355932203389</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F20" s="15">
         <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>57.142857142857</v>
+        <v>120</v>
       </c>
       <c r="I20" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="14">
-        <v>38.888888888888</v>
+        <v>57.894736842105</v>
       </c>
       <c r="L20" s="14">
-        <v>-45.652173913043</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="14">
-        <v>-35.897435897435</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.012779552715</v>
+        <v>-90.936555891238</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.181818181818</v>
+        <v>53.846153846153</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.126582278481</v>
+        <v>1.470588235294</v>
       </c>
       <c r="I21" s="17">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.510460251046</v>
+        <v>0.396825396825</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.684210526315</v>
+        <v>-38.141809290953</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.08038585209</v>
+        <v>-22.865853658536</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.041497152156</v>
+        <v>-80.833333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
@@ -1198,19 +1198,19 @@
         <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="15">
         <v>8</v>
       </c>
       <c r="K22" s="14">
+        <v>25</v>
+      </c>
+      <c r="L22" s="14">
+        <v>233.333333333333</v>
+      </c>
+      <c r="M22" s="14">
         <v>0</v>
-      </c>
-      <c r="L22" s="14">
-        <v>166.666666666667</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>84.615384615384</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G24" s="15">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>11.320754716981</v>
       </c>
       <c r="I24" s="15">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="J24" s="15">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.452736318407</v>
+        <v>-9.004739336492</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.296028880866</v>
+        <v>-34.693877551020</v>
       </c>
       <c r="M24" s="14">
-        <v>-9.452736318407</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15">
         <v>5</v>
       </c>
-      <c r="D25" s="15">
-        <v>6</v>
-      </c>
       <c r="E25" s="14">
-        <v>-16.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="14">
-        <v>-42.857142857142</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I25" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="15">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.373134328358</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>-63.235294117647</v>
+        <v>-64.084507042253</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
         <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="15">
         <v>51</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>64.516129032258</v>
+        <v>75.862068965517</v>
       </c>
       <c r="I26" s="15">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J26" s="15">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K26" s="14">
-        <v>30.081300813008</v>
+        <v>31.782945736434</v>
       </c>
       <c r="L26" s="14">
-        <v>31.147540983606</v>
+        <v>24.087591240875</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.614525139664</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,22 +1385,22 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
-      </c>
-      <c r="D27" s="15">
-        <v>3</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>5</v>
       </c>
       <c r="H27" s="14">
-        <v>-20</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
@@ -1426,22 +1426,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>8</v>
+      </c>
+      <c r="G28" s="15">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>9</v>
-      </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
       <c r="H28" s="14">
-        <v>80</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="15">
         <v>21</v>
@@ -1453,7 +1453,7 @@
         <v>40</v>
       </c>
       <c r="L28" s="14">
-        <v>31.25</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
+        <v>0</v>
+      </c>
+      <c r="L31" s="14">
         <v>50</v>
-      </c>
-      <c r="L31" s="14">
-        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -920,13 +920,13 @@
         <v>-14.285714285714</v>
       </c>
       <c r="L15" s="14">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N15" s="14">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
+        <v>6</v>
+      </c>
+      <c r="G16" s="15">
         <v>7</v>
       </c>
-      <c r="G16" s="15">
-        <v>8</v>
-      </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" s="14">
-        <v>-6.896551724137</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-41.304347826087</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="M16" s="14">
-        <v>-48.076923076923</v>
+        <v>-45.283018867924</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.8</v>
+        <v>-92.602040816326</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-87.5</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>27.777777777777</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I17" s="15">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J17" s="15">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K17" s="14">
-        <v>17.567567567567</v>
+        <v>8.536585365853</v>
       </c>
       <c r="L17" s="14">
-        <v>-7.446808510638</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="M17" s="14">
-        <v>77.551020408163</v>
+        <v>78</v>
       </c>
       <c r="N17" s="14">
-        <v>-41.216216216216</v>
+        <v>-44.025157232704</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>-20</v>
+        <v>60</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J18" s="15">
         <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-26.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-60</v>
+        <v>-55.357142857142</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.809523809523</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.432835820895</v>
+        <v>-92.877492877492</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F19" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-20.833333333333</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I19" s="15">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J19" s="15">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K19" s="14">
-        <v>-12.903225806451</v>
+        <v>-18.269230769230</v>
       </c>
       <c r="L19" s="14">
-        <v>-49.056603773584</v>
+        <v>-48.795180722891</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.829787234042</v>
+        <v>-14.141414141414</v>
       </c>
       <c r="N19" s="14">
-        <v>-31.355932203389</v>
+        <v>-34.108527131782</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>400</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>57.894736842105</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L20" s="14">
-        <v>-37.5</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="M20" s="14">
-        <v>-28.571428571428</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.936555891238</v>
+        <v>-90.857142857142</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>53.846153846153</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>1.470588235294</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="I21" s="17">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="J21" s="17">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="K21" s="18">
-        <v>0.396825396825</v>
+        <v>-3.272727272727</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.141809290953</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.865853658536</v>
+        <v>-21.994134897360</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.833333333333</v>
+        <v>-80.945558739255</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="14">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L22" s="14">
-        <v>233.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>9</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>-10</v>
+        <v>-55</v>
       </c>
       <c r="F24" s="15">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G24" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>11.320754716981</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I24" s="15">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="J24" s="15">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.004739336492</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.693877551020</v>
+        <v>-34.516129032258</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.513513513513</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="15">
         <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-40.909090909090</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J25" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K25" s="14">
-        <v>-29.166666666666</v>
+        <v>-33.75</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.084507042253</v>
+        <v>-64.429530201342</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14">
-        <v>83.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>75.862068965517</v>
+        <v>11.428571428571</v>
       </c>
       <c r="I26" s="15">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J26" s="15">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="K26" s="14">
-        <v>31.782945736434</v>
+        <v>17.687074829932</v>
       </c>
       <c r="L26" s="14">
-        <v>24.087591240875</v>
+        <v>19.310344827586</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.526315789473</v>
+        <v>-12.626262626262</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
         <v>12</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>166.666666666667</v>
+        <v>150</v>
       </c>
       <c r="I28" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="L28" s="14">
-        <v>10.526315789473</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="14">
         <v>-100</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L31" s="14">
         <v>50</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>100</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>-25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M15" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="N15" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,78 +937,78 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J16" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>-3.333333333333</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="L16" s="14">
-        <v>-40.816326530612</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="M16" s="14">
-        <v>-45.283018867924</v>
+        <v>-48.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.602040816326</v>
+        <v>-92.475728155339</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-87.5</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-23.809523809523</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="15">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J17" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K17" s="14">
-        <v>8.536585365853</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>-12.745098039215</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>78</v>
+        <v>60.714285714285</v>
       </c>
       <c r="N17" s="14">
-        <v>-44.025157232704</v>
+        <v>-46.428571428571</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="I18" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
         <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-16.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="14">
-        <v>-55.357142857142</v>
+        <v>-54.237288135593</v>
       </c>
       <c r="M18" s="14">
-        <v>-70.588235294117</v>
+        <v>-70.967741935483</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.877492877492</v>
+        <v>-92.931937172774</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-63.636363636363</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-44.827586206896</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="I19" s="15">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J19" s="15">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K19" s="14">
-        <v>-18.269230769230</v>
+        <v>-19.266055045871</v>
       </c>
       <c r="L19" s="14">
-        <v>-48.795180722891</v>
+        <v>-49.714285714285</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.141414141414</v>
+        <v>-16.190476190476</v>
       </c>
       <c r="N19" s="14">
-        <v>-34.108527131782</v>
+        <v>-35.294117647058</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
       <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I20" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="14">
-        <v>45.454545454545</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-39.622641509434</v>
+        <v>-45</v>
       </c>
       <c r="M20" s="14">
-        <v>-28.888888888888</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.857142857142</v>
+        <v>-90.934065934065</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-47.826086956521</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.178082191780</v>
+        <v>-15.492957746478</v>
       </c>
       <c r="I21" s="17">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="J21" s="17">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.272727272727</v>
+        <v>-3.819444444444</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.709677419354</v>
+        <v>-40.301724137931</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.994134897360</v>
+        <v>-25.135135135135</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.945558739255</v>
+        <v>-81.245768449559</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
       </c>
       <c r="D22" s="15">
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I22" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J22" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>22.222222222222</v>
+        <v>40</v>
       </c>
       <c r="L22" s="14">
-        <v>266.666666666667</v>
+        <v>180</v>
       </c>
       <c r="M22" s="14">
-        <v>-8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14">
-        <v>-55</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G24" s="15">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H24" s="14">
-        <v>-3.448275862068</v>
+        <v>20.370370370370</v>
       </c>
       <c r="I24" s="15">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="J24" s="15">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K24" s="14">
-        <v>-12.121212121212</v>
+        <v>-6.611570247933</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.516129032258</v>
+        <v>-30.030959752322</v>
       </c>
       <c r="M24" s="14">
-        <v>-17.142857142857</v>
+        <v>-13.076923076923</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-62.5</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G25" s="15">
         <v>24</v>
       </c>
       <c r="H25" s="14">
-        <v>-45.833333333333</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="15">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.75</v>
+        <v>-36.470588235294</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.429530201342</v>
+        <v>-64.473684210526</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D26" s="15">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-83.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>11.428571428571</v>
+        <v>2.380952380952</v>
       </c>
       <c r="I26" s="15">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="J26" s="15">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K26" s="14">
-        <v>17.687074829932</v>
+        <v>21.383647798742</v>
       </c>
       <c r="L26" s="14">
-        <v>19.310344827586</v>
+        <v>26.973684210526</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.626262626262</v>
+        <v>-8.095238095238</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,31 +1385,31 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>100</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="15">
         <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="I27" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="14">
-        <v>-16.666666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>43.75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>21.052631578947</v>
+        <v>26.315789473684</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="14">
         <v>-100</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="14">
         <v>50</v>

--- a/data/source/weekly/cs-en-us-072pct.xlsx
+++ b/data/source/weekly/cs-en-us-072pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="15">
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
+      <c r="H15" s="14">
         <v>100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
@@ -923,10 +923,10 @@
         <v>-11.111111111111</v>
       </c>
       <c r="M15" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,81 +934,81 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="14">
-        <v>-33.333333333333</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>60</v>
       </c>
       <c r="I16" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J16" s="15">
         <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>-6.060606060606</v>
+        <v>3.030303030303</v>
       </c>
       <c r="L16" s="14">
-        <v>-41.509433962264</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="M16" s="14">
-        <v>-48.333333333333</v>
+        <v>-46.031746031746</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.475728155339</v>
+        <v>-91.943127962085</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" s="14">
-        <v>-22.222222222222</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I17" s="15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J17" s="15">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" s="14">
-        <v>7.142857142857</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L17" s="14">
-        <v>-16.666666666666</v>
+        <v>-15.178571428571</v>
       </c>
       <c r="M17" s="14">
-        <v>60.714285714285</v>
+        <v>63.793103448275</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.428571428571</v>
+        <v>-48.924731182795</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>5</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="14">
+        <v>150</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
         <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-54.237288135593</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="14">
-        <v>-70.967741935483</v>
+        <v>-67.676767676767</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.931937172774</v>
+        <v>-92.118226600985</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15">
         <v>3</v>
       </c>
-      <c r="D19" s="15">
-        <v>5</v>
-      </c>
       <c r="E19" s="14">
-        <v>-40</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>-51.612903225806</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J19" s="15">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K19" s="14">
-        <v>-19.266055045871</v>
+        <v>-16.964285714285</v>
       </c>
       <c r="L19" s="14">
-        <v>-49.714285714285</v>
+        <v>-48.333333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>-16.190476190476</v>
+        <v>-17.699115044247</v>
       </c>
       <c r="N19" s="14">
-        <v>-35.294117647058</v>
+        <v>-36.734693877551</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>22.222222222222</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="15">
         <v>33</v>
       </c>
       <c r="J20" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>37.5</v>
+        <v>32</v>
       </c>
       <c r="L20" s="14">
         <v>-45</v>
@@ -1131,7 +1131,7 @@
         <v>-29.787234042553</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.934065934065</v>
+        <v>-91.315789473684</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.076923076923</v>
+        <v>157.142857142857</v>
       </c>
       <c r="F21" s="17">
         <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.492957746478</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.819444444444</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.301724137931</v>
+        <v>-38.923395445134</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.135135135135</v>
+        <v>-24.358974358974</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.245768449559</v>
+        <v>-81.101857783472</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
-      </c>
-      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>6</v>
+      </c>
+      <c r="G22" s="15">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
         <v>200</v>
       </c>
-      <c r="F22" s="15">
-        <v>5</v>
-      </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
-      <c r="H22" s="14">
-        <v>66.666666666666</v>
-      </c>
       <c r="I22" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="15">
         <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L22" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="M22" s="14">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>6.25</v>
       </c>
       <c r="F24" s="15">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G24" s="15">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H24" s="14">
-        <v>20.370370370370</v>
+        <v>1.754385964912</v>
       </c>
       <c r="I24" s="15">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="J24" s="15">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="K24" s="14">
-        <v>-6.611570247933</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="L24" s="14">
-        <v>-30.030959752322</v>
+        <v>-27.893175074184</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.076923076923</v>
+        <v>-12.274368231046</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="F25" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="15">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J25" s="15">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K25" s="14">
-        <v>-36.470588235294</v>
+        <v>-28.409090909090</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.473684210526</v>
+        <v>-60.625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
         <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H26" s="14">
-        <v>2.380952380952</v>
+        <v>2.083333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="J26" s="15">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="K26" s="14">
-        <v>21.383647798742</v>
+        <v>21.637426900584</v>
       </c>
       <c r="L26" s="14">
-        <v>26.973684210526</v>
+        <v>24.550898203592</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.095238095238</v>
+        <v>-5.022831050228</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>4</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>5</v>
-      </c>
-      <c r="G27" s="15">
-        <v>4</v>
-      </c>
       <c r="H27" s="14">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="I27" s="15">
         <v>12</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>133.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>24</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="15">
         <v>1</v>
       </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
         <v>4</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
         <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
